--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="389">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -79,10 +79,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -236,6 +233,15 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
+</t>
+  </si>
+  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1064,22 +1070,19 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>vbuffer</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>amux8</t>
+  </si>
+  <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>vbuffer</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -1600,7 +1603,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1620,7 +1623,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1640,7 +1643,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1655,7 +1658,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1673,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1690,12 +1693,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1710,12 +1713,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1730,12 +1733,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1753,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1765,131 +1768,136 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3518,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3616,7 +3624,7 @@
         <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3648,14 +3656,6 @@
         <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3671,85 +3671,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
         <v>345</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="I5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="K5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
-      </c>
-      <c r="M5" t="s">
-        <v>355</v>
       </c>
       <c r="N5" t="s">
         <v>72</v>
       </c>
       <c r="O5" t="s">
+        <v>355</v>
+      </c>
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="P5" t="s">
-        <v>357</v>
-      </c>
       <c r="Q5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3775,11 +3775,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3794,22 +3789,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3824,22 +3819,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3854,7 +3849,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3864,34 +3859,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3906,7 +3901,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3916,34 +3911,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3958,22 +3953,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3988,7 +3983,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4003,7 +3998,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4018,7 +4013,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4033,12 +4028,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4053,7 +4048,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4068,7 +4063,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4083,7 +4078,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4093,22 +4088,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4123,7 +4118,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4138,7 +4133,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4153,7 +4148,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4173,7 +4168,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4193,17 +4188,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4218,7 +4213,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4228,7 +4223,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4243,7 +4238,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4253,7 +4248,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4268,7 +4263,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4278,7 +4273,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4293,7 +4288,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4303,7 +4298,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4318,7 +4313,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="391">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -79,7 +79,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -234,10 +237,10 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
 4 error(s) during elaboration.
 </t>
   </si>
@@ -1070,6 +1073,9 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1082,7 +1088,7 @@
     <t>amux8</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -1603,7 +1609,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1623,7 +1629,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1643,7 +1649,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1658,7 +1664,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1673,7 +1679,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1693,12 +1699,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1713,12 +1719,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1733,12 +1739,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1759,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1773,132 +1779,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1913,7 +1919,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1958,17 +1964,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +1989,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2003,17 +2009,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2028,17 +2034,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2053,81 +2059,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2135,185 +2141,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2321,445 +2327,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2767,628 +2773,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B107" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B110" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B111" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B126" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B138" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B153" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B154" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B155" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B163" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B168" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B178" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3403,47 +3409,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3451,15 +3457,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3467,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3482,7 +3488,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3497,26 +3503,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3526,12 +3532,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3541,122 +3547,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3671,85 +3685,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>354</v>
+      </c>
+      <c r="K5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
-        <v>352</v>
-      </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
       <c r="L5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3773,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3775,6 +3789,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3789,22 +3808,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3819,22 +3838,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3849,44 +3868,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3901,44 +3920,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3953,22 +3972,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +4002,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3998,7 +4017,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4013,12 +4032,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4028,12 +4047,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4067,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +4082,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4078,7 +4097,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4088,22 +4107,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4118,12 +4137,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4133,7 +4152,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4148,12 +4167,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4168,12 +4187,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4188,17 +4207,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -4213,7 +4232,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4223,7 +4242,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4238,7 +4257,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4248,7 +4267,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4263,7 +4282,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4273,7 +4292,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4288,7 +4307,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4298,7 +4317,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +4332,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="389">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,10 +64,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -236,15 +233,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1052,10 +1040,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
-  </si>
-  <si>
-    <t>noconn</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1609,7 +1597,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1629,7 +1617,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1649,7 +1637,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1664,7 +1652,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1667,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1699,12 +1687,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1719,12 +1707,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1739,12 +1727,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1747,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1774,137 +1762,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1919,7 +1902,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1964,17 +1947,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1989,7 +1972,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2009,17 +1992,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2034,17 +2017,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2059,81 +2042,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2141,185 +2124,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2327,445 +2310,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2773,628 +2756,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3409,47 +3392,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3457,15 +3440,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3473,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3488,7 +3471,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3503,26 +3486,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3537,7 +3520,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3547,130 +3530,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3685,85 +3668,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="I5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
       </c>
-      <c r="K5" t="s">
-        <v>351</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>355</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="N5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O5" t="s">
-        <v>357</v>
-      </c>
-      <c r="P5" t="s">
-        <v>358</v>
-      </c>
       <c r="Q5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3808,22 +3791,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3838,22 +3821,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3868,44 +3851,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3920,44 +3903,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3972,22 +3955,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4002,7 +3985,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4017,7 +4000,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4032,12 +4015,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4047,12 +4030,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4050,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4082,7 +4065,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4112,17 +4095,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4137,12 +4120,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4152,7 +4135,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4167,12 +4150,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4187,12 +4170,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4207,17 +4190,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4232,7 +4215,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4242,7 +4225,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4257,7 +4240,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4267,7 +4250,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4282,7 +4265,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4292,7 +4275,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4307,7 +4290,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4317,7 +4300,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4332,7 +4315,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="390">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -230,6 +230,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1762,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1888,6 +1897,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1902,7 +1916,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1947,17 +1961,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1972,7 +1986,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1992,17 +2006,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2017,17 +2031,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2042,81 +2056,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2124,185 +2138,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2310,445 +2324,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2756,628 +2770,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3392,47 +3406,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3440,15 +3454,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3456,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3471,7 +3485,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3486,26 +3500,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3520,7 +3534,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3530,130 +3544,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3668,85 +3682,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H5" t="s">
+        <v>352</v>
+      </c>
+      <c r="I5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
-        <v>348</v>
-      </c>
-      <c r="F5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>353</v>
+      </c>
+      <c r="K5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
-        <v>352</v>
-      </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
       <c r="L5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -3791,22 +3805,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3821,22 +3835,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3851,44 +3865,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3903,44 +3917,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3955,22 +3969,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +3999,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4000,7 +4014,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4015,12 +4029,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4030,12 +4044,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4050,7 +4064,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4065,7 +4079,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4120,12 +4134,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4135,7 +4149,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4150,12 +4164,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4170,12 +4184,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4190,17 +4204,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="389">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -230,15 +230,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1771,7 +1762,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1897,11 +1888,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1916,7 +1902,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1961,17 +1947,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1986,7 +1972,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2006,17 +1992,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2031,17 +2017,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2056,81 +2042,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2138,185 +2124,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2324,445 +2310,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2770,628 +2756,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3406,47 +3392,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3454,15 +3440,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3470,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3485,7 +3471,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3500,26 +3486,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3534,7 +3520,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3544,130 +3530,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3682,85 +3668,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
         <v>345</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="I5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="K5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>355</v>
       </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="P5" t="s">
-        <v>357</v>
-      </c>
       <c r="Q5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3805,22 +3791,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3835,22 +3821,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3865,44 +3851,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3917,44 +3903,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3969,22 +3955,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3999,7 +3985,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4014,7 +4000,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4029,12 +4015,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4044,12 +4030,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4064,7 +4050,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4079,7 +4065,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4134,12 +4120,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4149,7 +4135,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4164,12 +4150,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4184,12 +4170,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4204,17 +4190,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="388">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,31 +64,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1040,10 +1040,13 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>nand2</t>
+    <t>PEBBLEtielo</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1061,9 +1064,6 @@
     <t>dbuf</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1074,9 +1074,6 @@
   </si>
   <si>
     <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -3515,7 +3512,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3557,7 +3554,7 @@
         <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3565,7 +3562,7 @@
         <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3573,7 +3570,7 @@
         <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3645,14 +3642,6 @@
         <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>338</v>
-      </c>
-      <c r="B19" t="s">
         <v>311</v>
       </c>
     </row>
@@ -3668,85 +3657,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s">
         <v>344</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>345</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>349</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" t="s">
         <v>352</v>
       </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>353</v>
-      </c>
-      <c r="M5" t="s">
-        <v>354</v>
       </c>
       <c r="N5" t="s">
         <v>71</v>
       </c>
       <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
         <v>355</v>
       </c>
-      <c r="P5" t="s">
-        <v>356</v>
-      </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3756,7 +3745,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3772,11 +3761,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3791,22 +3775,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3821,22 +3805,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3851,7 +3835,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3861,34 +3845,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3903,7 +3887,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3913,34 +3897,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3955,22 +3939,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4000,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +3999,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4030,12 +4014,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4050,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4065,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4080,7 +4064,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4090,12 +4074,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4120,7 +4104,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4135,7 +4119,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4150,7 +4134,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4170,7 +4154,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4190,17 +4174,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="389">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -230,6 +230,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -1759,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1885,6 +1893,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1912,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1944,17 +1957,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1969,7 +1982,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1989,17 +2002,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2014,17 +2027,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2039,81 +2052,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2121,185 +2134,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2307,445 +2320,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2753,628 +2766,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3389,47 +3402,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3437,15 +3450,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3453,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3468,7 +3481,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3483,26 +3496,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3517,7 +3530,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3527,122 +3540,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3657,85 +3670,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I5" t="s">
         <v>346</v>
       </c>
-      <c r="E5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>352</v>
+      </c>
+      <c r="K5" t="s">
         <v>349</v>
       </c>
-      <c r="H5" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J5" t="s">
-        <v>351</v>
-      </c>
-      <c r="K5" t="s">
-        <v>348</v>
-      </c>
       <c r="L5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3775,22 +3788,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3805,22 +3818,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3835,44 +3848,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3887,44 +3900,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3939,22 +3952,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3982,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +3997,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3999,12 +4012,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4014,12 +4027,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4034,7 +4047,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4049,7 +4062,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4104,12 +4117,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4119,7 +4132,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4134,12 +4147,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4154,12 +4167,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4174,17 +4187,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -234,10 +234,11 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="388">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -230,15 +230,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1768,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1894,11 +1885,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1913,7 +1899,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1958,17 +1944,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +1969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2003,17 +1989,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2028,17 +2014,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2053,81 +2039,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2135,185 +2121,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2321,445 +2307,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2767,628 +2753,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3403,47 +3389,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3451,15 +3437,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3467,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3482,7 +3468,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3497,26 +3483,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3531,7 +3517,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3541,122 +3527,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3671,85 +3657,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s">
         <v>344</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>345</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>349</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" t="s">
         <v>352</v>
       </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>353</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>354</v>
       </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>355</v>
       </c>
-      <c r="P5" t="s">
-        <v>356</v>
-      </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3789,22 +3775,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3819,22 +3805,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3849,44 +3835,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3901,44 +3887,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3953,22 +3939,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3998,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4013,12 +3999,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4028,12 +4014,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4118,12 +4104,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4133,7 +4119,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4148,12 +4134,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4168,12 +4154,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4188,17 +4174,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="391">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -230,6 +236,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1594,7 +1609,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1614,7 +1629,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1634,7 +1649,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1649,7 +1664,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1679,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1684,12 +1699,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1704,12 +1719,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1724,12 +1739,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1759,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1759,132 +1774,137 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1919,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1944,17 +1964,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1969,7 +1989,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1989,17 +2009,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2014,17 +2034,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2039,81 +2059,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2121,185 +2141,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2307,445 +2327,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2753,628 +2773,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
+        <v>217</v>
+      </c>
+      <c r="B124" t="s">
         <v>214</v>
-      </c>
-      <c r="B124" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3389,47 +3409,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3437,15 +3457,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3453,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3468,7 +3488,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3483,26 +3503,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3517,7 +3537,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3527,122 +3547,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3657,85 +3677,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
         <v>348</v>
       </c>
-      <c r="G5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H5" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" t="s">
-        <v>345</v>
-      </c>
       <c r="J5" t="s">
+        <v>354</v>
+      </c>
+      <c r="K5" t="s">
         <v>351</v>
       </c>
-      <c r="K5" t="s">
-        <v>348</v>
-      </c>
       <c r="L5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="R5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3775,22 +3795,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3805,22 +3825,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3835,44 +3855,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3887,44 +3907,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3939,22 +3959,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3989,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +4004,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3999,12 +4019,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4014,12 +4034,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4034,7 +4054,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4049,7 +4069,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4059,7 +4079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4090,6 +4110,16 @@
     <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4104,12 +4134,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4119,7 +4149,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4134,12 +4164,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4154,12 +4184,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4174,17 +4204,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -4199,7 +4229,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4209,7 +4239,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4224,7 +4254,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4234,7 +4264,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4249,7 +4279,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4259,7 +4289,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4274,7 +4304,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4284,7 +4314,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4299,7 +4329,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="387">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,10 +64,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -239,15 +230,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1055,28 +1037,28 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
   </si>
   <si>
-    <t>noconn</t>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>switchgnd</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>dbuf</t>
   </si>
   <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>switchgnd</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>dbuf</t>
   </si>
   <si>
     <t>vbuffer</t>
@@ -1609,7 +1591,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1629,7 +1611,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1649,7 +1631,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1664,7 +1646,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1661,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1699,12 +1681,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1719,12 +1701,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1739,12 +1721,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1741,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1774,137 +1756,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1919,7 +1896,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1964,17 +1941,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1989,7 +1966,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2009,17 +1986,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2034,17 +2011,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2059,81 +2036,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2141,185 +2118,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2327,445 +2304,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2773,628 +2750,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B101" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B118" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B122" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B124" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B128" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B129" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B130" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B132" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B133" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B134" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B135" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B136" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B137" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B138" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B139" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B140" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B146" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B147" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B149" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B150" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B152" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B153" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B156" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B158" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B159" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B160" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B161" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B162" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B163" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B164" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B166" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B167" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B168" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B169" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B171" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B172" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B173" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B174" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B175" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B176" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B177" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B178" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3409,47 +3386,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3457,15 +3434,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3473,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3488,7 +3465,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3503,26 +3480,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3537,7 +3514,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3547,122 +3524,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3677,85 +3654,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" t="s">
         <v>346</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>347</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
         <v>348</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>349</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
+        <v>344</v>
+      </c>
+      <c r="J5" t="s">
         <v>350</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
+        <v>347</v>
+      </c>
+      <c r="L5" t="s">
         <v>351</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>352</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" t="s">
         <v>353</v>
       </c>
-      <c r="I5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>354</v>
       </c>
-      <c r="K5" t="s">
-        <v>351</v>
-      </c>
-      <c r="L5" t="s">
-        <v>355</v>
-      </c>
-      <c r="M5" t="s">
-        <v>356</v>
-      </c>
-      <c r="N5" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" t="s">
-        <v>357</v>
-      </c>
-      <c r="P5" t="s">
-        <v>358</v>
-      </c>
       <c r="Q5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -3795,22 +3772,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3825,22 +3802,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3855,44 +3832,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3907,44 +3884,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3959,22 +3936,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3989,7 +3966,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -4004,7 +3981,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4019,12 +3996,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4034,12 +4011,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4054,7 +4031,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4069,7 +4046,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4079,7 +4056,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4099,27 +4076,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4134,12 +4101,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4149,7 +4116,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4164,12 +4131,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4184,12 +4151,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4204,17 +4171,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -4229,7 +4196,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4239,7 +4206,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4254,7 +4221,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4264,7 +4231,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4279,7 +4246,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4289,7 +4256,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4304,7 +4271,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4314,7 +4281,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4296,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="388">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,28 +64,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1037,10 +1040,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
-  </si>
-  <si>
-    <t>nand2</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1591,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1611,7 +1614,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1631,7 +1634,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1646,7 +1649,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1661,7 +1664,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1681,12 +1684,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1701,12 +1704,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1721,12 +1724,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1744,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1761,127 +1764,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1896,7 +1899,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1941,17 +1944,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1966,7 +1969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1986,17 +1989,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2011,17 +2014,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2036,81 +2039,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2118,185 +2121,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2304,445 +2307,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2750,628 +2753,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3386,47 +3389,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3434,15 +3437,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3450,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3465,7 +3468,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3480,26 +3483,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3514,7 +3517,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3524,122 +3527,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3654,85 +3657,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" t="s">
         <v>345</v>
       </c>
-      <c r="E5" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K5" t="s">
         <v>348</v>
       </c>
-      <c r="H5" t="s">
-        <v>349</v>
-      </c>
-      <c r="I5" t="s">
-        <v>344</v>
-      </c>
-      <c r="J5" t="s">
-        <v>350</v>
-      </c>
-      <c r="K5" t="s">
-        <v>347</v>
-      </c>
       <c r="L5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3772,22 +3775,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3802,22 +3805,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3832,44 +3835,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -3884,44 +3887,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -3936,22 +3939,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3966,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3981,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3996,12 +3999,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4011,12 +4014,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4031,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4046,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4076,17 +4079,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4101,12 +4104,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4116,7 +4119,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4131,12 +4134,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4151,12 +4154,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4171,17 +4174,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -4196,7 +4199,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4206,7 +4209,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4221,7 +4224,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4231,7 +4234,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4246,7 +4249,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4256,7 +4259,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4271,7 +4274,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4281,7 +4284,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4296,7 +4299,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Sanity.xlsx
+++ b/GPIpuget/project/Sanity.xlsx
@@ -416,7 +416,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/GPIpuget.net</t>
+    <t>/portal/web/api/utils/hopper/tests/GPIpuget.net</t>
   </si>
   <si>
     <t>gen_reports</t>
